--- a/artfynd/A 10171-2024 artfynd.xlsx
+++ b/artfynd/A 10171-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3468,6 +3468,123 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120086484</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>654272</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7008426</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10171-2024 artfynd.xlsx
+++ b/artfynd/A 10171-2024 artfynd.xlsx
@@ -3473,7 +3473,7 @@
         <v>120086484</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
